--- a/giro_da_praça_ofertas - BIRITÃO.xlsx
+++ b/giro_da_praça_ofertas - BIRITÃO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4162BF0-507C-4B1D-B860-0B2B766E47C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D375600B-F569-463F-8F1F-0F3887552F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -677,7 +677,8 @@
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="7">
-        <v>2.89</v>
+        <f>15*2.89</f>
+        <v>43.35</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
